--- a/samples/clover/design-data/xlsx/Jokers.xlsx
+++ b/samples/clover/design-data/xlsx/Jokers.xlsx
@@ -90,7 +90,7 @@
     <t xml:space="preserve">희귀도</t>
   </si>
   <si>
-    <t xml:space="preserve">상점에서의 값</t>
+    <t xml:space="preserve">상점에서의 가격</t>
   </si>
   <si>
     <t xml:space="preserve">표시 이름</t>
